--- a/artfynd/A 31885-2024 artfynd.xlsx
+++ b/artfynd/A 31885-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120647876</v>
+        <v>120645060</v>
       </c>
       <c r="B2" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580853</v>
+        <v>580964</v>
       </c>
       <c r="R2" t="n">
-        <v>7076153</v>
+        <v>7076227</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120645269</v>
+        <v>120645010</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580956</v>
+        <v>580974</v>
       </c>
       <c r="R3" t="n">
-        <v>7076195</v>
+        <v>7076209</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120647645</v>
+        <v>120647611</v>
       </c>
       <c r="B4" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mettjärnen, Mettjärnen, Ång</t>
+          <t>Mettjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580864</v>
+        <v>580908</v>
       </c>
       <c r="R4" t="n">
-        <v>7076130</v>
+        <v>7076132</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120647900</v>
+        <v>120647876</v>
       </c>
       <c r="B5" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580859</v>
+        <v>580853</v>
       </c>
       <c r="R5" t="n">
-        <v>7076177</v>
+        <v>7076153</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120645886</v>
+        <v>120682276</v>
       </c>
       <c r="B6" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mettjärnen, Mettjärnen, Ång</t>
+          <t>Mettjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580901</v>
+        <v>580846</v>
       </c>
       <c r="R6" t="n">
-        <v>7076147</v>
+        <v>7076148</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1158,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,53 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120645500</v>
+        <v>120682652</v>
       </c>
       <c r="B7" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mettjärnen, Mettjärnen, Ång</t>
+          <t>Mettjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580913</v>
+        <v>580809</v>
       </c>
       <c r="R7" t="n">
-        <v>7076171</v>
+        <v>7076191</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1260,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120645538</v>
+        <v>120645500</v>
       </c>
       <c r="B8" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580895</v>
+        <v>580913</v>
       </c>
       <c r="R8" t="n">
-        <v>7076150</v>
+        <v>7076171</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,54 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120645251</v>
+        <v>120645538</v>
       </c>
       <c r="B9" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mettjärnen, Mettjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580956</v>
+        <v>580895</v>
       </c>
       <c r="R9" t="n">
-        <v>7076199</v>
+        <v>7076150</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,54 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120646699</v>
+        <v>120645886</v>
       </c>
       <c r="B10" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mettjärnen, Mettjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580895</v>
+        <v>580901</v>
       </c>
       <c r="R10" t="n">
-        <v>7076113</v>
+        <v>7076147</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1606,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120647711</v>
+        <v>120646067</v>
       </c>
       <c r="B11" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580840</v>
+        <v>580905</v>
       </c>
       <c r="R11" t="n">
-        <v>7076125</v>
+        <v>7076148</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1708,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120647611</v>
+        <v>120647505</v>
       </c>
       <c r="B12" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1724,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1748,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580908</v>
+        <v>580898</v>
       </c>
       <c r="R12" t="n">
-        <v>7076132</v>
+        <v>7076129</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1810,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120647505</v>
+        <v>120647645</v>
       </c>
       <c r="B13" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,14 +1773,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mettjärnen, Ång</t>
+          <t>Mettjärnen, Mettjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580898</v>
+        <v>580864</v>
       </c>
       <c r="R13" t="n">
-        <v>7076129</v>
+        <v>7076130</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120646067</v>
+        <v>120647711</v>
       </c>
       <c r="B14" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580905</v>
+        <v>580840</v>
       </c>
       <c r="R14" t="n">
-        <v>7076148</v>
+        <v>7076125</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2017,12 +1939,7 @@
         <v>120647804</v>
       </c>
       <c r="B15" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120682434</v>
+        <v>120647900</v>
       </c>
       <c r="B16" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,34 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mettjärnen, Ång</t>
+          <t>Mettjärnen, Mettjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580804</v>
+        <v>580859</v>
       </c>
       <c r="R16" t="n">
-        <v>7076166</v>
+        <v>7076177</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2186,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2221,12 +2133,7 @@
         <v>120681667</v>
       </c>
       <c r="B17" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120683032</v>
+        <v>120682756</v>
       </c>
       <c r="B18" t="n">
-        <v>79711</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2363,7 +2265,7 @@
         <v>580823</v>
       </c>
       <c r="R18" t="n">
-        <v>7076214</v>
+        <v>7076187</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2422,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120682652</v>
+        <v>120683398</v>
       </c>
       <c r="B19" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,37 +2335,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mettjärnen, Ång</t>
+          <t>Mettjärnen, Mettjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580809</v>
+        <v>580757</v>
       </c>
       <c r="R19" t="n">
-        <v>7076191</v>
+        <v>7076230</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2524,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120682756</v>
+        <v>120683032</v>
       </c>
       <c r="B20" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,7 +2459,7 @@
         <v>580823</v>
       </c>
       <c r="R20" t="n">
-        <v>7076187</v>
+        <v>7076214</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2626,50 +2518,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120682276</v>
+        <v>120645269</v>
       </c>
       <c r="B21" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mettjärnen, Ång</t>
+          <t>Mettjärnen, Mettjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580846</v>
+        <v>580956</v>
       </c>
       <c r="R21" t="n">
-        <v>7076148</v>
+        <v>7076195</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2696,12 +2583,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2728,15 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120683398</v>
+        <v>120682434</v>
       </c>
       <c r="B22" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2744,34 +2631,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mettjärnen, Mettjärnen, Ång</t>
+          <t>Mettjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580757</v>
+        <v>580804</v>
       </c>
       <c r="R22" t="n">
-        <v>7076230</v>
+        <v>7076166</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2827,6 +2714,208 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120645251</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mettjärnen, Mettjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>580956</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7076199</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120646699</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mettjärnen, Mettjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>580895</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7076113</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Michaela Ehmann</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31885-2024 artfynd.xlsx
+++ b/artfynd/A 31885-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120645060</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120645010</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120647611</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120647876</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682276</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682652</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120645500</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120645538</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120645886</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120646067</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120647505</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120647645</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120647711</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120647804</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120647900</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120681667</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682756</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683398</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120683032</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120645269</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120682434</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2815,6 +2925,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120645251</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2916,8 +3031,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120646699</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>